--- a/copilot/examples/01_formulas.xlsx
+++ b/copilot/examples/01_formulas.xlsx
@@ -1154,10 +1154,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What Copilot gives with files 11 and 12 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet before you try the workbook on Copilot yourself.</t>
-        </is>
-      </c>
-    </row>
+          <t>What Copilot gives with files 11, 12, 03, 04 and 05 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet, and the Power Query sheet if there is one, before you try the workbook on Copilot yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1165,6 +1166,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
